--- a/Result/profitability/2235.xlsx
+++ b/Result/profitability/2235.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM60"/>
+  <dimension ref="A1:AM61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.77</v>
       </c>
       <c r="M2" t="n">
-        <v>0.4025</v>
+        <v>0.35</v>
       </c>
       <c r="N2" t="n">
-        <v>19.09875</v>
+        <v>17.92</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.85</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4325000000000001</v>
+        <v>0.37875</v>
       </c>
       <c r="N3" t="n">
-        <v>18.52625</v>
+        <v>17.65125</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -8050,6 +8050,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2235</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>147</v>
+      </c>
+      <c r="D61" t="n">
+        <v>124</v>
+      </c>
+      <c r="E61" t="n">
+        <v>22</v>
+      </c>
+      <c r="F61" t="n">
+        <v>15.16</v>
+      </c>
+      <c r="G61" t="n">
+        <v>2</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>1.57%</t>
+        </is>
+      </c>
+      <c r="I61" t="n">
+        <v>7</v>
+      </c>
+      <c r="J61" t="n">
+        <v>9</v>
+      </c>
+      <c r="K61" t="n">
+        <v>7</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="N61" t="n">
+        <v>18.72375</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>0</v>
+      </c>
+      <c r="R61" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" t="n">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>0</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
+      </c>
+      <c r="V61" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W61" t="n">
+        <v>-0.08000000000000002</v>
+      </c>
+      <c r="X61" t="n">
+        <v>-0.2962962962962963</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>0.6500000000000004</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>0.04479669193659541</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="AB61" t="n">
+        <v>-1.41304347826087</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>-4.289999999999999</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>-0.2205655526992287</v>
+      </c>
+      <c r="AE61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF61" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG61" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK61" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL61" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM61" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
